--- a/registration_forms/030_focus_group_facilitation_training_registration--registration_forms.xlsx
+++ b/registration_forms/030_focus_group_facilitation_training_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'contact_person_1',_'label':_'person_1'}</t>
+          <t>person_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'contact_person_1', 'label': 'Person 1'}</t>
+          <t>Person 1</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'contact_person_2',_'label':_'person_2'}</t>
+          <t>person_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'contact_person_2', 'label': 'Person 2'}</t>
+          <t>Person 2</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'contact_person_3',_'label':_'person_3'}</t>
+          <t>person_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'contact_person_3', 'label': 'Person 3'}</t>
+          <t>Person 3</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'beginner',_'label':_'beginner'}</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'beginner', 'label': 'Beginner'}</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'intermediate',_'label':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'intermediate', 'label': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'advanced',_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'advanced', 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
